--- a/src/api/media/excel/export_org_tmpl.xlsx
+++ b/src/api/media/excel/export_org_tmpl.xlsx
@@ -1,73 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiananzhang/workspace/devcloud_file/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E846F-F60C-9940-A9F4-B16BD1ADDBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="user_info" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>用户名</t>
-  </si>
-  <si>
-    <t>邮箱</t>
-  </si>
-  <si>
-    <t>手机号</t>
-  </si>
-  <si>
-    <t>组织</t>
-  </si>
-  <si>
-    <t>微信</t>
-  </si>
-  <si>
-    <t>职务</t>
-  </si>
-  <si>
-    <t>QQ</t>
-  </si>
-  <si>
-    <t>全名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>上级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>账户状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在职状态</t>
-  </si>
-  <si>
-    <t>账号过期时间</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>填写须知：
     1、表头代表用户字段，每行数据代表一个用户。</t>
     </r>
@@ -124,6 +86,7 @@
         <charset val="134"/>
       </rPr>
       <t>。
+    8、操作类型：（覆盖/新增）, 控制组织归属的处理方式。当出现非法值的时候，默认新增。（当采用覆盖模式的时候，清空用户现有的所有组织，替换为 Excel 中指定的组织）（当采用新增模式的时候，保留用户现有的组织，在此基础上追加 Excel 中指定的组织）
 Instructions for filling out:
     1. The table header represents user fields, and each row of data represents a user. The username field cannot be added, deleted or modified, and must be exactly the same as in the user management.å
     2. Fields with red names are required fields, while those with black names are optional.
@@ -131,17 +94,69 @@
     4. Organization: Separate superior and subordinate organizations using '/', starting from the highest level organization; separate multiple organizations using commas (,), with individual organization names not exceeding 32 characters in length. If an organizational link does not exist it will be automatically created.
     5. Mobile phone number: Default area code is +86 (CN) for China region; other regions need to add country/region codes in this format "+85259****24".
     6. Direct supervisor: Fill in the superior's username (username); separate multiple superiors using commas (,).
-    7. Custom fields: For enumerated values please fill in option values; use commas to separate multiple selections.</t>
+    7. Custom fields: For enumerated values please fill in option values; use commas to separate multiple selections.
+    8. Operation type: (Overwrite/Add). This determines how the organizational affiliation of the user is handled. If an invalid value occurs, the add mode will be used. (In overwrite mode, all existing organizations of the user will be cleared and replaced with the organizations specified in the Excel file.) (In add mode, the user's existing organizations will be retained, and the organizations specified in the Excel file will be added on top.)</t>
     </r>
+  </si>
+  <si>
+    <t>用户名</t>
+  </si>
+  <si>
+    <t>全名</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>手机号</t>
+  </si>
+  <si>
+    <t>账户状态</t>
+  </si>
+  <si>
+    <t>在职状态</t>
+  </si>
+  <si>
+    <t>组织</t>
+  </si>
+  <si>
+    <t>账号过期时间</t>
+  </si>
+  <si>
+    <t>微信</t>
+  </si>
+  <si>
+    <t>职务</t>
+  </si>
+  <si>
+    <t>QQ</t>
+  </si>
+  <si>
+    <t>上级</t>
+  </si>
+  <si>
+    <t>操作类型</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -149,47 +164,176 @@
       <b/>
       <sz val="18"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -206,15 +350,201 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -222,9 +552,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -235,57 +807,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -607,386 +1223,388 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.33203125" style="8" customWidth="1"/>
-    <col min="7" max="8" width="28.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22" style="3" customWidth="1"/>
-    <col min="10" max="10" width="39.1640625" style="8" customWidth="1"/>
-    <col min="11" max="11" width="17" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.3333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.6666666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.6666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.3333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.8333333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.3333333333333" style="3" customWidth="1"/>
+    <col min="7" max="8" width="28.6666666666667" style="4" customWidth="1"/>
+    <col min="9" max="9" width="22" style="4" customWidth="1"/>
+    <col min="10" max="10" width="39.1666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="409" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="409" customHeight="1" spans="1:13">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:13">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
+      <c r="M2" s="13" t="s">
+        <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="9"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="9"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="9"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="9"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="9"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="9"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="9"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="9"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="9"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="9"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="9"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="9"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="9"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="9"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="9"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="9"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="9"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="9"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="9"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="9"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="9"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="J23" s="3"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="9"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="9"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="J25" s="3"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="9"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="9"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="9"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="9"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="J29" s="3"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="9"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="9"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="9"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="9"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="9"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="9"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.510416666666667" footer="0.510416666666667"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>